--- a/output/pdf_financials_xlsx/CUU.xlsx
+++ b/output/pdf_financials_xlsx/CUU.xlsx
@@ -1300,43 +1300,43 @@
         <v>1.614027</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5.363615</v>
+        <v>-3.898689</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.179924</v>
+        <v>-3.238472</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>1.281668</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.350909</v>
+        <v>-1.350909</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.546398</v>
+        <v>-1.546398</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.070949</v>
+        <v>-1.070949</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.200857</v>
+        <v>-1.200857</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.368128</v>
+        <v>-1.368128</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.626031</v>
+        <v>-2.626031</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.861228</v>
+        <v>-0.861228</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.290966</v>
+        <v>-1.290966</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.114512</v>
+        <v>-1.114512</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.607303</v>
+        <v>-0.607303</v>
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-2.274982</v>
+        <v>-3.74841</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-4.618912</v>
+        <v>-61.66812</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.228054</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.732463</v>
@@ -1595,52 +1595,52 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.736714</v>
+        <v>-0.736714</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>28.524604</v>
+        <v>-28.524604</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.614027</v>
+        <v>-1.614027</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.631152</v>
+        <v>-4.631152</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.209198</v>
+        <v>-3.209198</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>1.281668</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.350909</v>
+        <v>-1.350909</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.546398</v>
+        <v>-1.546398</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.070949</v>
+        <v>-1.070949</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.200857</v>
+        <v>-1.200857</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.368128</v>
+        <v>-1.368128</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.626031</v>
+        <v>-2.626031</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.861228</v>
+        <v>-0.861228</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.290966</v>
+        <v>-1.290966</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.114512</v>
+        <v>-1.114512</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.607303</v>
+        <v>-0.607303</v>
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
@@ -1775,52 +1775,52 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.736714</v>
+        <v>-0.736714</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>28.524604</v>
+        <v>-28.524604</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.614027</v>
+        <v>-1.614027</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.631152</v>
+        <v>-4.631152</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.209198</v>
+        <v>-3.209198</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>1.281668</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.350909</v>
+        <v>-1.350909</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.546398</v>
+        <v>-1.546398</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.070949</v>
+        <v>-1.070949</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.200857</v>
+        <v>-1.200857</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.368128</v>
+        <v>-1.368128</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.626031</v>
+        <v>-2.626031</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.861228</v>
+        <v>-0.861228</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.290966</v>
+        <v>-1.290966</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.114512</v>
+        <v>-1.114512</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.607303</v>
+        <v>-0.607303</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>-1.071237</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-150.129495</v>
+        <v>150.129495</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2052,43 +2052,43 @@
         <v>1.614027</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.363615</v>
+        <v>-3.898689</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.179924</v>
+        <v>-3.238472</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>1.281668</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.350909</v>
+        <v>-1.350909</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.546398</v>
+        <v>-1.546398</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.070949</v>
+        <v>-1.070949</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.200857</v>
+        <v>-1.200857</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.368128</v>
+        <v>-1.368128</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.626031</v>
+        <v>-2.626031</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.861228</v>
+        <v>-0.861228</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.290966</v>
+        <v>-1.290966</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.114512</v>
+        <v>-1.114512</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.607303</v>
+        <v>-0.607303</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2172,43 +2172,43 @@
         <v>1.614027</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.363615</v>
+        <v>-3.898689</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.179924</v>
+        <v>-3.238472</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>1.281668</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.350909</v>
+        <v>-1.350909</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.546398</v>
+        <v>-1.546398</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.070949</v>
+        <v>-1.070949</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.200857</v>
+        <v>-1.200857</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.368128</v>
+        <v>-1.368128</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.626031</v>
+        <v>-2.626031</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.861228</v>
+        <v>-0.861228</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.290966</v>
+        <v>-1.290966</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.131194</v>
+        <v>-1.09783</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.620756</v>
+        <v>-0.59385</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2315,52 +2315,52 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>75.53823493473445</v>
+        <v>124.4617650652656</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>13.93609537382817</v>
+        <v>186.0639046261718</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>13.6561442236253</v>
+        <v>-18.78741802693162</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.9205880392110001</v>
+        <v>-0.9039448233611407</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.105076</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.543026</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>2.071709</v>
@@ -5962,19 +5962,19 @@
         <v>15.823771</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>15.823771</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>15.823771</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>15.823771</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>15.823771</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>15.823771</v>
       </c>
     </row>
     <row r="93">
@@ -10860,7 +10860,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -20503,7 +20507,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -42748,10 +42756,10 @@
         </is>
       </c>
       <c r="K347" s="5" t="n">
-        <v>1.350909</v>
+        <v>-1.350909</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>1.546398</v>
+        <v>-1.546398</v>
       </c>
       <c r="M347" t="inlineStr">
         <is>
@@ -42774,13 +42782,13 @@
         </is>
       </c>
       <c r="Q347" s="5" t="n">
-        <v>0.861228</v>
+        <v>-0.861228</v>
       </c>
       <c r="R347" s="5" t="n">
-        <v>1.290966</v>
+        <v>-1.290966</v>
       </c>
       <c r="S347" s="5" t="n">
-        <v>1.114512</v>
+        <v>-1.114512</v>
       </c>
       <c r="T347" s="5" t="n">
         <v>0.607303</v>
@@ -47479,13 +47487,13 @@
         </is>
       </c>
       <c r="Q394" s="5" t="n">
-        <v>1.800995</v>
+        <v>-1.800995</v>
       </c>
       <c r="R394" s="5" t="n">
-        <v>0.188067</v>
+        <v>-0.188067</v>
       </c>
       <c r="S394" s="5" t="n">
-        <v>0.787152</v>
+        <v>-0.787152</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -50412,19 +50420,19 @@
         </is>
       </c>
       <c r="L424" s="5" t="n">
-        <v>1.546398</v>
+        <v>-1.546398</v>
       </c>
       <c r="M424" s="5" t="n">
-        <v>1.070949</v>
+        <v>-1.070949</v>
       </c>
       <c r="N424" s="5" t="n">
-        <v>1.200857</v>
+        <v>-1.200857</v>
       </c>
       <c r="O424" s="5" t="n">
-        <v>1.368128</v>
+        <v>-1.368128</v>
       </c>
       <c r="P424" s="5" t="n">
-        <v>2.626031</v>
+        <v>-2.626031</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -55739,10 +55747,10 @@
         </is>
       </c>
       <c r="K478" s="5" t="n">
-        <v>1.350909</v>
+        <v>-1.350909</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>1.546398</v>
+        <v>-1.546398</v>
       </c>
       <c r="M478" t="inlineStr">
         <is>
@@ -57617,10 +57625,10 @@
         </is>
       </c>
       <c r="H497" s="5" t="n">
-        <v>4.631152</v>
+        <v>-4.631152</v>
       </c>
       <c r="I497" s="5" t="n">
-        <v>3.209198</v>
+        <v>-3.209198</v>
       </c>
       <c r="J497" t="inlineStr">
         <is>
@@ -58299,16 +58307,16 @@
         </is>
       </c>
       <c r="E504" s="5" t="n">
-        <v>0.736714</v>
+        <v>-0.736714</v>
       </c>
       <c r="F504" s="5" t="n">
-        <v>28.524604</v>
+        <v>-28.524604</v>
       </c>
       <c r="G504" s="5" t="n">
-        <v>1.614027</v>
+        <v>-1.614027</v>
       </c>
       <c r="H504" s="5" t="n">
-        <v>3.882381</v>
+        <v>-3.882381</v>
       </c>
       <c r="I504" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CUU.xlsx
+++ b/output/pdf_financials_xlsx/CUU.xlsx
@@ -1051,28 +1051,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.116214</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00033</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000225</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000478</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025641</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.056976</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.122362</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -2043,28 +2043,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.011696</v>
+        <v>3.12791</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>33.143516</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.614027</v>
+        <v>1.614357</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.898689</v>
+        <v>-3.898464</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.238472</v>
+        <v>-3.237994</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.281668</v>
+        <v>1.307309</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.350909</v>
+        <v>-1.293933</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.546398</v>
+        <v>-1.424036</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-1.070949</v>
@@ -2163,28 +2163,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.011696</v>
+        <v>3.12791</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>33.143516</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.614027</v>
+        <v>1.614357</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.898689</v>
+        <v>-3.898464</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.238472</v>
+        <v>-3.237994</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.281668</v>
+        <v>1.307309</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.350909</v>
+        <v>-1.293933</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.546398</v>
+        <v>-1.424036</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-1.070949</v>
@@ -2498,10 +2498,10 @@
         <v>1.529138</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.847505</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.286195</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.938311</v>
@@ -2614,10 +2614,10 @@
         <v>1.529138</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.847505</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.286195</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.938311</v>
@@ -3310,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.863688</v>
+        <v>0.016183</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.286195</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -7789,19 +7789,19 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.029678</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.029678</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032376</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032376</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02164</v>
       </c>
     </row>
     <row r="125">
@@ -7847,19 +7847,19 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.029678</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.029678</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032376</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032376</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02164</v>
       </c>
     </row>
     <row r="126">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -28417,7 +28417,11 @@
           <t>Office lease payments</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -31561,7 +31565,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -55016,7 +55024,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E471" s="5" t="n">
@@ -56616,7 +56624,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">

--- a/output/pdf_financials_xlsx/CUU.xlsx
+++ b/output/pdf_financials_xlsx/CUU.xlsx
@@ -1309,34 +1309,34 @@
         <v>1.281668</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-1.350909</v>
+        <v>-2.733444</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.546398</v>
+        <v>-1.910352</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.070949</v>
+        <v>-1.667161</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-1.200857</v>
+        <v>-1.456055</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.368128</v>
+        <v>-1.633028</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-2.626031</v>
+        <v>-2.727188</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.861228</v>
+        <v>-1.115228</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-1.290966</v>
+        <v>-1.350966</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-1.114512</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-0.607303</v>
+        <v>-1.088214</v>
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
@@ -1369,34 +1369,34 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>1.382535</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0.363954</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0.596212</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>0.255198</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>0.2649</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>0.101157</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>0.254</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>0.480911</v>
       </c>
       <c r="R17" s="1" t="inlineStr">
         <is>
@@ -2061,34 +2061,34 @@
         <v>1.307309</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.293933</v>
+        <v>-2.676468</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.424036</v>
+        <v>-1.78799</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.070949</v>
+        <v>-1.667161</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.200857</v>
+        <v>-1.456055</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.368128</v>
+        <v>-1.633028</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.626031</v>
+        <v>-2.727188</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.861228</v>
+        <v>-1.115228</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.290966</v>
+        <v>-1.350966</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-1.114512</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.607303</v>
+        <v>-1.088214</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2181,34 +2181,34 @@
         <v>1.307309</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.293933</v>
+        <v>-2.676468</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.424036</v>
+        <v>-1.78799</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.070949</v>
+        <v>-1.667161</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.200857</v>
+        <v>-1.456055</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.368128</v>
+        <v>-1.633028</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.626031</v>
+        <v>-2.727188</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.861228</v>
+        <v>-1.115228</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.290966</v>
+        <v>-1.350966</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-1.09783</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.59385</v>
+        <v>-1.074761</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2333,34 +2333,34 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-50.57850096800959</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-19.05167215256665</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-35.76211295729686</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-17.52667309957385</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-16.22139975554614</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.709205232642561</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-22.77561180314698</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.441266471547026</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-44.19268636499806</v>
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>0.005454</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.030558</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -26984,7 +26984,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -31466,7 +31470,11 @@
           <t>Net proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -32555,7 +32563,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -35416,7 +35428,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -47330,7 +47346,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -50288,7 +50308,11 @@
           <t>Deferred income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -51757,7 +51781,11 @@
           <t>Deferred income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -55119,7 +55147,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
